--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T09:04:56+00:00</t>
+    <t>2024-02-19T13:34:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T13:34:28+00:00</t>
+    <t>2024-02-19T13:42:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T13:42:29+00:00</t>
+    <t>2024-03-04T16:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$15</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="166">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-04T16:55:03+00:00</t>
+    <t>2024-03-05T15:34:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -336,6 +336,84 @@
     <t>Optional Extension Element - found in all resources.</t>
   </si>
   <si>
+    <t>ContactPoint.extension:emailType.id</t>
+  </si>
+  <si>
+    <t>ContactPoint.extension.id</t>
+  </si>
+  <si>
+    <t>ContactPoint.extension:emailType.extension</t>
+  </si>
+  <si>
+    <t>ContactPoint.extension.extension</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t>ContactPoint.extension:emailType.url</t>
+  </si>
+  <si>
+    <t>ContactPoint.extension.url</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uri
+</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>http://interopsante.org/fhir/StructureDefinition/FrContactPointEmailType</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>ContactPoint.extension:emailType.value[x]</t>
+  </si>
+  <si>
+    <t>ContactPoint.extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="https://mos.esante.gouv.fr/NOS/TRE_R256-TypeMessagerie/FHIR/TRE-R256-TypeMessagerie"/&gt;
+  &lt;code value="MSSANTE"/&gt;
+&lt;/valueCoding&gt;</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>http://interopsante.org/fhir/ValueSet/fr-email-type</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
     <t>ContactPoint.extension:as-mailbox-mss-metadata</t>
   </si>
   <si>
@@ -385,10 +463,6 @@
   <si>
     <t>ele-1
 cpt-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-</t>
   </si>
   <si>
     <t>ContactPoint.value</t>
@@ -778,11 +852,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ11"/>
+  <dimension ref="A1:AJ15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="46.90625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="22.34765625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="31.8984375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="24.98828125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="12.64453125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -806,7 +880,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="41.33984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="45.71875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="46.91015625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -1241,7 +1315,7 @@
         <v>99</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
@@ -1268,9 +1342,7 @@
       <c r="M5" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="N5" t="s" s="2">
-        <v>92</v>
-      </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>73</v>
@@ -1339,11 +1411,9 @@
         <v>103</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="C6" t="s" s="2">
         <v>104</v>
       </c>
+      <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
         <v>73</v>
       </c>
@@ -1364,13 +1434,13 @@
         <v>73</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1421,27 +1491,27 @@
         <v>73</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>97</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1449,10 +1519,10 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>73</v>
@@ -1461,20 +1531,18 @@
         <v>73</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N7" s="2"/>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
         <v>73</v>
@@ -1484,7 +1552,7 @@
         <v>73</v>
       </c>
       <c r="S7" t="s" s="2">
-        <v>114</v>
+        <v>73</v>
       </c>
       <c r="T7" t="s" s="2">
         <v>73</v>
@@ -1499,51 +1567,51 @@
         <v>73</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="Y7" t="s" s="2">
-        <v>116</v>
+        <v>73</v>
       </c>
       <c r="Z7" t="s" s="2">
-        <v>117</v>
+        <v>73</v>
       </c>
       <c r="AA7" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AD7" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>119</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1557,35 +1625,33 @@
         <v>82</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="O8" t="s" s="2">
-        <v>124</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
         <v>73</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>73</v>
+        <v>115</v>
       </c>
       <c r="S8" t="s" s="2">
         <v>73</v>
@@ -1627,27 +1693,27 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="AH8" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>119</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1664,26 +1730,22 @@
         <v>73</v>
       </c>
       <c r="I9" t="s" s="2">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="O9" t="s" s="2">
-        <v>129</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>73</v>
       </c>
@@ -1692,7 +1754,7 @@
         <v>73</v>
       </c>
       <c r="S9" t="s" s="2">
-        <v>73</v>
+        <v>122</v>
       </c>
       <c r="T9" t="s" s="2">
         <v>73</v>
@@ -1707,13 +1769,11 @@
         <v>73</v>
       </c>
       <c r="X9" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="Y9" t="s" s="2">
-        <v>130</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="Y9" s="2"/>
       <c r="Z9" t="s" s="2">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="AA9" t="s" s="2">
         <v>73</v>
@@ -1743,17 +1803,19 @@
         <v>79</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>119</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>87</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>128</v>
+      </c>
       <c r="D10" t="s" s="2">
         <v>73</v>
       </c>
@@ -1771,20 +1833,18 @@
         <v>73</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="N10" s="2"/>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>73</v>
@@ -1833,27 +1893,27 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>132</v>
+        <v>96</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>119</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1861,7 +1921,7 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>82</v>
@@ -1873,19 +1933,19 @@
         <v>73</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -1896,7 +1956,7 @@
         <v>73</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>73</v>
+        <v>138</v>
       </c>
       <c r="T11" t="s" s="2">
         <v>73</v>
@@ -1911,13 +1971,13 @@
         <v>73</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>73</v>
+        <v>139</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>73</v>
+        <v>140</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>73</v>
+        <v>141</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>73</v>
@@ -1935,7 +1995,7 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -1944,14 +2004,426 @@
         <v>82</v>
       </c>
       <c r="AI11" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AJ11" t="s" s="2">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="12" hidden="true">
+      <c r="A12" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H12" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="I12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J12" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="K12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="O12" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="P12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q12" s="2"/>
+      <c r="R12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF12" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AG12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI12" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="AJ11" t="s" s="2">
-        <v>142</v>
+      <c r="AJ12" t="s" s="2">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="13" hidden="true">
+      <c r="A13" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I13" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="J13" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="K13" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="O13" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="P13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q13" s="2"/>
+      <c r="R13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X13" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF13" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="14" hidden="true">
+      <c r="A14" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E14" s="2"/>
+      <c r="F14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J14" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="K14" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O14" s="2"/>
+      <c r="P14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q14" s="2"/>
+      <c r="R14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF14" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="15" hidden="true">
+      <c r="A15" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J15" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="K15" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="O15" s="2"/>
+      <c r="P15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q15" s="2"/>
+      <c r="R15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF15" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
+        <v>165</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ11">
+  <autoFilter ref="A1:AJ15">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -1961,7 +2433,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI10">
+  <conditionalFormatting sqref="A2:AI14">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-05T15:34:40+00:00</t>
+    <t>2024-03-06T10:45:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T10:45:14+00:00</t>
+    <t>2024-03-07T10:27:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -424,7 +424,7 @@
 </t>
   </si>
   <si>
-    <t>AS Mailbox Metadata</t>
+    <t>Les attributs 'responsible' et 'phone' ne sont pas disponibles en accès libre.</t>
   </si>
   <si>
     <t>Extension contenant les métadonnées de la mailbox mss.</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-07T10:27:01+00:00</t>
+    <t>2024-03-12T12:54:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T12:54:34+00:00</t>
+    <t>2024-03-12T13:20:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:20:54+00:00</t>
+    <t>2024-03-12T13:39:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:39:01+00:00</t>
+    <t>2024-03-12T13:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:58:30+00:00</t>
+    <t>2024-03-12T14:02:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:02:45+00:00</t>
+    <t>2024-03-12T14:08:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:08:02+00:00</t>
+    <t>2024-03-12T14:13:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:13:18+00:00</t>
+    <t>2024-03-12T14:29:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:29:58+00:00</t>
+    <t>2024-03-12T16:57:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T16:57:02+00:00</t>
+    <t>2024-03-12T17:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T17:28:16+00:00</t>
+    <t>2024-03-13T08:21:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,13 +60,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T08:21:45+00:00</t>
+    <t>2024-03-13T15:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>ANS</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Contact</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T15:21:15+00:00</t>
+    <t>2024-03-13T15:40:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T15:40:01+00:00</t>
+    <t>2024-03-15T14:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T13:53:07+00:00</t>
+    <t>2024-04-02T14:01:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-ballot-4</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T14:01:28+00:00</t>
+    <t>2024-04-03T13:55:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T12:41:20+00:00</t>
+    <t>2024-04-08T12:53:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T12:53:48+00:00</t>
+    <t>2024-04-09T07:46:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-09T07:46:55+00:00</t>
+    <t>2024-04-10T12:18:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T12:18:24+00:00</t>
+    <t>2024-04-10T12:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:21:45+00:00</t>
+    <t>2024-04-18T13:43:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T13:43:00+00:00</t>
+    <t>2024-04-25T11:33:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:10:14+00:00</t>
+    <t>2024-06-03T16:22:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:22:01+00:00</t>
+    <t>2024-06-03T16:23:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:23:50+00:00</t>
+    <t>2024-06-03T16:30:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:30:34+00:00</t>
+    <t>2024-06-05T12:07:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-05T12:07:44+00:00</t>
+    <t>2024-06-07T15:57:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-07T15:57:22+00:00</t>
+    <t>2024-07-01T19:46:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T19:46:33+00:00</t>
+    <t>2024-07-09T08:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T08:44:23+00:00</t>
+    <t>2024-07-10T09:54:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1</t>
+    <t>1.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T09:54:14+00:00</t>
+    <t>2024-07-10T10:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:00:25+00:00</t>
+    <t>2024-07-10T10:02:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:02:38+00:00</t>
+    <t>2024-07-10T10:13:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:13:33+00:00</t>
+    <t>2024-07-10T12:01:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T12:01:49+00:00</t>
+    <t>2024-07-10T12:37:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T12:37:24+00:00</t>
+    <t>2024-07-10T13:09:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:09:17+00:00</t>
+    <t>2024-07-10T13:09:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:09:58+00:00</t>
+    <t>2024-07-10T13:27:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:27:13+00:00</t>
+    <t>2024-07-11T14:15:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T14:15:05+00:00</t>
+    <t>2024-07-11T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0-snapshot</t>
+    <t>1.1.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T14:20:03+00:00</t>
+    <t>2024-07-11T15:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T15:32:47+00:00</t>
+    <t>2024-07-11T15:43:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T15:43:40+00:00</t>
+    <t>2024-07-11T16:04:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T16:04:15+00:00</t>
+    <t>2024-07-12T06:54:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-12T06:54:28+00:00</t>
+    <t>2024-07-12T07:24:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-27T17:01:01+00:00</t>
+    <t>2025-01-31T09:33:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T09:33:18+00:00</t>
+    <t>2025-02-03T16:26:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T16:26:04+00:00</t>
+    <t>2025-02-11T12:19:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -473,10 +473,7 @@
   </si>
   <si>
     <t>typeBAL : Type de boîte aux lettres.
-Valeurs possibles :
-ORG pour une BAL organisationnelle;
-APP pour une BAL applicative;
-PER pour une BAL personnelle, rattachée à une personne physique</t>
+Valeurs possibles : ORG | APP | PER | CAB</t>
   </si>
   <si>
     <t>ContactPoint.extension:as-mailbox-mss-metadata.extension:type.id</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:19:13+00:00</t>
+    <t>2025-02-11T12:46:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:46:26+00:00</t>
+    <t>2025-02-11T13:37:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T13:37:59+00:00</t>
+    <t>2025-02-11T14:09:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T14:09:44+00:00</t>
+    <t>2025-02-11T15:57:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T15:57:50+00:00</t>
+    <t>2025-02-11T16:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T16:04:30+00:00</t>
+    <t>2025-02-11T16:35:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-17T22:39:20+00:00</t>
+    <t>2025-02-24T08:37:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T08:37:03+00:00</t>
+    <t>2025-02-27T14:21:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T14:21:41+00:00</t>
+    <t>2025-02-27T14:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T14:23:05+00:00</t>
+    <t>2025-02-28T10:02:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T10:02:48+00:00</t>
+    <t>2025-03-05T17:59:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-05T17:59:44+00:00</t>
+    <t>2025-03-06T14:41:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T14:41:30+00:00</t>
+    <t>2025-03-06T14:56:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T14:56:25+00:00</t>
+    <t>2025-03-12T15:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T15:24:25+00:00</t>
+    <t>2025-03-18T14:02:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T14:02:39+00:00</t>
+    <t>2025-03-18T16:59:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T16:59:29+00:00</t>
+    <t>2025-03-21T10:50:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-1</t>
+    <t>1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:01:00+00:00</t>
+    <t>2026-06-19T13:53:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.2.0</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -343,14 +343,16 @@
     <t>emailType</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point-email-type|2.1.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point-email-type|2.2.0}
 </t>
   </si>
   <si>
     <t>Type of email | type de messagerie électronique</t>
   </si>
   <si>
-    <t>Extension on the ContactPoint datatype. This extension allows to specify the type of mail used to contact the person (MSSsanté|Apicrypt|OSM|Autre).</t>
+    <t>Extension permettant d'indiquer le type d'adresse email d'un ContactPoint.
++ This extension allows to specify the type of mail used to contact the person.</t>
   </si>
   <si>
     <t>boiteLettresMSS.typeBAL</t>
@@ -421,7 +423,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-email-type|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-email-type|2.2.0</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -437,7 +439,7 @@
     <t>as-mailbox-mss-metadata</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata|1.2.0-snapshot-2}
 </t>
   </si>
   <si>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T13:53:04+00:00</t>
+    <t>2026-06-19T14:07:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T14:07:56+00:00</t>
+    <t>2026-06-23T09:20:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T09:20:47+00:00</t>
+    <t>2026-06-23T12:21:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T12:21:55+00:00</t>
+    <t>2026-06-26T10:36:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T10:36:05+00:00</t>
+    <t>2026-06-27T10:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-27T10:35:23+00:00</t>
+    <t>2026-06-30T07:59:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T07:59:11+00:00</t>
+    <t>2026-07-10T15:33:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-2</t>
+    <t>1.2.0-snapshot-3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T15:33:23+00:00</t>
+    <t>2026-07-10T15:46:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -439,7 +439,7 @@
     <t>as-mailbox-mss-metadata</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata|1.2.0-snapshot-3}
 </t>
   </si>
   <si>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T15:46:03+00:00</t>
+    <t>2026-08-03T13:23:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T13:23:25+00:00</t>
+    <t>2026-08-03T14:28:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T14:28:09+00:00</t>
+    <t>2026-08-04T08:16:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-mailbox-mss.xlsx
+++ b/main/ig/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T08:16:57+00:00</t>
+    <t>2026-08-04T12:10:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
